--- a/results/3er_zivlaw.xlsx
+++ b/results/3er_zivlaw.xlsx
@@ -477,13 +477,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C4" t="n">
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>6.896551724137931</v>
+        <v>6.451612903225806</v>
       </c>
     </row>
   </sheetData>
